--- a/erp-server/erp-server-srm/src/main/resources/excel/poReconciliationDetail.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/poReconciliationDetail.xlsx
@@ -4,19 +4,82 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>单据单号</t>
+  </si>
+  <si>
+    <t>采购单号</t>
+  </si>
+  <si>
+    <t>单据类型</t>
+  </si>
+  <si>
+    <t>供应商名称</t>
+  </si>
+  <si>
+    <t>业务状态</t>
+  </si>
+  <si>
+    <t>确认日期</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>产品名称</t>
+  </si>
+  <si>
+    <t>送货数量</t>
+  </si>
+  <si>
+    <t>收货数量</t>
+  </si>
+  <si>
+    <t>税率</t>
+  </si>
+  <si>
+    <t>含税单价</t>
+  </si>
+  <si>
+    <t>价税合计</t>
+  </si>
+  <si>
+    <t>结算组织</t>
+  </si>
+  <si>
+    <t>结算方式</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -941,9 +1004,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="10.75" customWidth="1"/>
+    <col min="2" max="2" width="10.375" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="13.75" customWidth="1"/>
+    <col min="5" max="5" width="11.5" customWidth="1"/>
+    <col min="6" max="6" width="15.25" customWidth="1"/>
+    <col min="8" max="8" width="13.625" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="11.875" customWidth="1"/>
+    <col min="12" max="13" width="12.125" customWidth="1"/>
+    <col min="14" max="14" width="13.125" customWidth="1"/>
+    <col min="15" max="15" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/erp-server/erp-server-srm/src/main/resources/excel/poReconciliationDetail.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/poReconciliationDetail.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>单据单号</t>
   </si>
@@ -74,6 +74,63 @@
   </si>
   <si>
     <t>结算方式</t>
+  </si>
+  <si>
+    <t>付款条件</t>
+  </si>
+  <si>
+    <t>是否加入账单</t>
+  </si>
+  <si>
+    <t>{.sourceCode}</t>
+  </si>
+  <si>
+    <t>{.poCode}</t>
+  </si>
+  <si>
+    <t>{.sourceTypeName}</t>
+  </si>
+  <si>
+    <t>{.supplierName}</t>
+  </si>
+  <si>
+    <t>{.businessStatusName}</t>
+  </si>
+  <si>
+    <t>{.confirmDate}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.deliveryQty}</t>
+  </si>
+  <si>
+    <t>{.receiveQty}</t>
+  </si>
+  <si>
+    <t>{.taxRateStr}</t>
+  </si>
+  <si>
+    <t>{.taxPrice}</t>
+  </si>
+  <si>
+    <t>{.taxAmount}</t>
+  </si>
+  <si>
+    <t>{.settleOrgName}</t>
+  </si>
+  <si>
+    <t>{.settleDictName}</t>
+  </si>
+  <si>
+    <t>{.paymentConditionName}</t>
+  </si>
+  <si>
+    <t>{.isAddAccountStr}</t>
   </si>
 </sst>
 </file>
@@ -1004,24 +1061,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Q2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="10.75" customWidth="1"/>
-    <col min="2" max="2" width="10.375" customWidth="1"/>
-    <col min="3" max="3" width="10.875" customWidth="1"/>
-    <col min="4" max="4" width="13.75" customWidth="1"/>
-    <col min="5" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="6" width="15.25" customWidth="1"/>
-    <col min="8" max="8" width="13.625" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="14.125" customWidth="1"/>
+    <col min="3" max="3" width="15.375" customWidth="1"/>
+    <col min="4" max="4" width="20.25" customWidth="1"/>
+    <col min="5" max="5" width="15.625" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="15.25" customWidth="1"/>
+    <col min="8" max="8" width="18.5" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="11.875" customWidth="1"/>
-    <col min="12" max="13" width="12.125" customWidth="1"/>
-    <col min="14" max="14" width="13.125" customWidth="1"/>
-    <col min="15" max="15" width="10.625" customWidth="1"/>
+    <col min="10" max="10" width="14.5" customWidth="1"/>
+    <col min="11" max="12" width="12.125" customWidth="1"/>
+    <col min="13" max="13" width="14.875" customWidth="1"/>
+    <col min="14" max="14" width="21.875" customWidth="1"/>
+    <col min="15" max="15" width="15.375" customWidth="1"/>
+    <col min="16" max="16" width="17.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1066,6 +1126,65 @@
       </c>
       <c r="O1" t="s">
         <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
